--- a/Account_Setup_and_Data_Load_-_PM&C_JVREVJUL25toJUN26_Setup.xlsx
+++ b/Account_Setup_and_Data_Load_-_PM&C_JVREVJUL25toJUN26_Setup.xlsx
@@ -5788,7 +5788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -6282,7 +6282,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>4. Coverage — please confirm before loading: of the five JVs, only BIA currently appears as a revenue line in the loaded FY26 figures (Account_Setup_and_Data_Load_-_PM&amp;C_REVJUL25toJUN26_Setup.xlsx, and the "FY26 Rev" detail). Allied Asphalt, EDI Rail-Bombardier Transportation, Emulco and Isaac Asphalt do not appear in those revenue figures at all, so posting negatives for them reduces reported revenue by amounts that were never included (FY26: BIA 69.9 of the 128.4 total; the other four total 58.5: Allied Asphalt 11.6, EDI Rail-Bombardier 35.6, Emulco 4.2, Isaac Asphalt 7.1).</t>
+          <t>4. Coverage — CONFIRMED 4 Aug 26: all five JVs are to be uploaded as negatives. For reference: of the five, only BIA appears as a revenue line in the loaded FY26 figures (Account_Setup_and_Data_Load_-_PM&amp;C_REVJUL25toJUN26_Setup.xlsx, and the "FY26 Rev" detail); Allied Asphalt, EDI Rail-Bombardier Transportation, Emulco and Isaac Asphalt do not appear in those figures, so their negatives reduce reported revenue by amounts not previously included (FY26: BIA 69.9 of the 128.4 total; the other four total 58.5: Allied Asphalt 11.6, EDI Rail-Bombardier 35.6, Emulco 4.2, Isaac Asphalt 7.1).</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,14 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>5. Also note: "Rail Services Victoria Pty Ltd" (Keolis Downer JV) IS in the loaded FY26 revenue figures under REV_Keolis Downer JV (FY26 total 27.3), but is not listed on the "FY26 JV Rev" source sheet, so it is not excluded by this file. Confirm whether it should be.</t>
+          <t>5. Keolis Downer JV — CONFIRMED 4 Aug 26: not excluded. "Rail Services Victoria Pty Ltd" IS in the loaded FY26 revenue figures under REV_Keolis Downer JV (FY26 total 27.3) but is not on the "FY26 JV Rev" source sheet; the source sheet is the agreed definition of JV revenue to exclude, so it stays in revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>6. BIA Location Ref: the extract shows Location Ref "RSV175-1" for _CLOSED_REV_BIA, which looks like a Rail Services Victoria code. Copied faithfully from the extract; worth confirming with the Envizi admin when reopening the locations.</t>
         </is>
       </c>
     </row>

--- a/Account_Setup_and_Data_Load_-_PM&C_JVREVJUL25toJUN26_Setup.xlsx
+++ b/Account_Setup_and_Data_Load_-_PM&C_JVREVJUL25toJUN26_Setup.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Account_Setup_and_Data_Load" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="FY26 JV Revenue" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Monthly Totals Check" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Check - By JV by Month" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Prep - with formulas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="FY26 JV Rev" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FY26 JV Revenue" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monthly Totals Check" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Check - By JV by Month" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,12 +21,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\-#,##0.0;\-"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0\ ;\(#,##0.0\);&quot;- &quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;\(#,##0.0\);&quot;-&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +39,22 @@
     <font>
       <name val="Aptos Narrow"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -63,12 +83,18 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.7999816888943144"/>
+        <bgColor theme="4" tint="0.7999816888943144"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -96,7 +122,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -104,30 +130,74 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.3999755851924192"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.3999755851924192"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.3999755851924192"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.3999755851924192"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.3999755851924192"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.3999755851924192"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.3999755851924192"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.3999755851924192"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5788,6 +5858,5393 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:T61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37.42578125" customWidth="1" min="3" max="3"/>
+    <col width="16.5703125" customWidth="1" min="4" max="4"/>
+    <col width="21.28515625" customWidth="1" min="6" max="6"/>
+    <col width="25.5703125" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="51.28515625" customWidth="1" min="9" max="9"/>
+    <col width="13.140625" customWidth="1" min="12" max="12"/>
+    <col width="12.85546875" customWidth="1" min="13" max="13"/>
+    <col width="21.42578125" customWidth="1" min="17" max="17"/>
+    <col width="64.85546875" customWidth="1" min="18" max="18"/>
+    <col width="24.140625" customWidth="1" min="19" max="19"/>
+    <col width="9.140625" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Organization Link</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Location Ref</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Account Style Link</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Account Style Caption</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Account Subtype</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Account Number</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Account Reference</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Account Supplier</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Account Reader</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Record Start YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Record End YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Record Data Quality</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Record Billing Type</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Record Subtype</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Record Entry Method</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Record Reference</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Record Invoice Number</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C2" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D2" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H2" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I2" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R2" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S2" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T2" s="3">
+        <f>-'FY26 JV Rev'!B2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C3" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D3" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H3" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I3" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R3" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S3" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T3" s="3">
+        <f>-'FY26 JV Rev'!B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C4" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D4" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H4" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I4" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R4" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S4" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T4" s="3">
+        <f>-'FY26 JV Rev'!B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C5" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H5" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q5" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R5" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S5" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T5" s="3">
+        <f>-'FY26 JV Rev'!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C6" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H6" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R6" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S6" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T6" s="3">
+        <f>-'FY26 JV Rev'!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C7" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D7" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H7" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I7" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R7" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S7" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T7" s="3">
+        <f>-'FY26 JV Rev'!C2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C8" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D8" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H8" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I8" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R8" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S8" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T8" s="3">
+        <f>-'FY26 JV Rev'!C3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C9" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D9" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H9" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I9" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q9" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R9" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S9" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T9" s="3">
+        <f>-'FY26 JV Rev'!C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C10" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D10" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H10" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I10" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q10" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R10" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S10" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T10" s="3">
+        <f>-'FY26 JV Rev'!C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C11" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D11" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H11" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I11" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R11" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S11" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T11" s="3">
+        <f>-'FY26 JV Rev'!C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C12" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D12" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H12" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I12" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q12" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R12" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S12" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T12" s="3">
+        <f>-'FY26 JV Rev'!D2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C13" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D13" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H13" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I13" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q13" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R13" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S13" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T13" s="3">
+        <f>-'FY26 JV Rev'!D3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C14" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D14" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H14" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I14" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R14" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S14" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T14" s="3">
+        <f>-'FY26 JV Rev'!D4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C15" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D15" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H15" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I15" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O15" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q15" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R15" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S15" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T15" s="3">
+        <f>-'FY26 JV Rev'!D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C16" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D16" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H16" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I16" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q16" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R16" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S16" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T16" s="3">
+        <f>-'FY26 JV Rev'!D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C17" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D17" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H17" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I17" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q17" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R17" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S17" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T17" s="3">
+        <f>-'FY26 JV Rev'!E2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C18" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D18" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H18" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I18" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O18" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q18" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R18" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S18" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T18" s="3">
+        <f>-'FY26 JV Rev'!E3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C19" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D19" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H19" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I19" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N19" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O19" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q19" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R19" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S19" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T19" s="3">
+        <f>-'FY26 JV Rev'!E4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C20" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D20" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H20" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I20" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q20" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R20" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S20" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T20" s="3">
+        <f>-'FY26 JV Rev'!E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C21" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D21" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H21" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I21" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="N21" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q21" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R21" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S21" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T21" s="3">
+        <f>-'FY26 JV Rev'!E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C22" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D22" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H22" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I22" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="N22" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q22" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R22" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S22" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T22" s="3">
+        <f>-'FY26 JV Rev'!F2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C23" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D23" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H23" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I23" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="N23" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O23" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q23" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R23" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S23" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T23" s="3">
+        <f>-'FY26 JV Rev'!F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C24" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D24" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H24" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I24" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="N24" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O24" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q24" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R24" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S24" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T24" s="3">
+        <f>-'FY26 JV Rev'!F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C25" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D25" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H25" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I25" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="N25" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O25" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q25" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R25" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S25" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T25" s="3">
+        <f>-'FY26 JV Rev'!F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C26" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D26" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H26" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I26" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="N26" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O26" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q26" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R26" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S26" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T26" s="3">
+        <f>-'FY26 JV Rev'!F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C27" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D27" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H27" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I27" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="N27" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q27" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R27" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S27" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T27" s="3">
+        <f>-'FY26 JV Rev'!G2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C28" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D28" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H28" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I28" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="N28" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q28" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R28" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S28" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T28" s="3">
+        <f>-'FY26 JV Rev'!G3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C29" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D29" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H29" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I29" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="N29" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O29" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q29" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R29" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S29" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T29" s="3">
+        <f>-'FY26 JV Rev'!G4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C30" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D30" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H30" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I30" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q30" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R30" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S30" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T30" s="3">
+        <f>-'FY26 JV Rev'!G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C31" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D31" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H31" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I31" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="N31" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q31" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R31" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S31" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T31" s="3">
+        <f>-'FY26 JV Rev'!G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C32" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D32" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H32" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I32" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q32" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R32" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S32" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T32" s="3">
+        <f>-'FY26 JV Rev'!H2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C33" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D33" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H33" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I33" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J33" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="N33" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q33" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R33" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S33" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T33" s="3">
+        <f>-'FY26 JV Rev'!H3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C34" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D34" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H34" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I34" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q34" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R34" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S34" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T34" s="3">
+        <f>-'FY26 JV Rev'!H4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C35" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D35" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H35" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I35" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="N35" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q35" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R35" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S35" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T35" s="3">
+        <f>-'FY26 JV Rev'!H5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C36" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D36" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H36" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I36" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="N36" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q36" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R36" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S36" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T36" s="3">
+        <f>-'FY26 JV Rev'!H6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C37" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D37" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H37" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I37" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J37" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="N37" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q37" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R37" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S37" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T37" s="3">
+        <f>-'FY26 JV Rev'!I2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C38" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D38" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H38" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I38" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="N38" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q38" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R38" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S38" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T38" s="3">
+        <f>-'FY26 JV Rev'!I3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C39" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D39" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H39" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I39" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J39" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="N39" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q39" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R39" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S39" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T39" s="3">
+        <f>-'FY26 JV Rev'!I4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C40" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D40" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H40" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I40" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="N40" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q40" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R40" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S40" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T40" s="3">
+        <f>-'FY26 JV Rev'!I5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C41" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D41" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H41" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I41" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="N41" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q41" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R41" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S41" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T41" s="3">
+        <f>-'FY26 JV Rev'!I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C42" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D42" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H42" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I42" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="N42" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q42" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R42" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S42" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T42" s="3">
+        <f>-'FY26 JV Rev'!J2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C43" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D43" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H43" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I43" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J43" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="N43" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q43" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R43" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S43" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T43" s="3">
+        <f>-'FY26 JV Rev'!J3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C44" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D44" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H44" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I44" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="N44" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q44" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R44" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S44" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T44" s="3">
+        <f>-'FY26 JV Rev'!J4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C45" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D45" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H45" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I45" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J45" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="N45" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q45" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R45" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S45" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T45" s="3">
+        <f>-'FY26 JV Rev'!J5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C46" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D46" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H46" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I46" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="N46" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q46" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R46" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S46" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T46" s="3">
+        <f>-'FY26 JV Rev'!J6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C47" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D47" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H47" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I47" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="N47" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q47" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R47" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S47" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T47" s="3">
+        <f>-'FY26 JV Rev'!K2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C48" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D48" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H48" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I48" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J48" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="N48" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q48" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R48" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S48" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T48" s="3">
+        <f>-'FY26 JV Rev'!K3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C49" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D49" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H49" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I49" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q49" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R49" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S49" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T49" s="3">
+        <f>-'FY26 JV Rev'!K4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C50" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D50" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H50" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I50" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K50" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q50" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R50" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S50" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T50" s="3">
+        <f>-'FY26 JV Rev'!K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C51" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D51" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H51" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I51" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q51" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R51" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S51" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T51" s="3">
+        <f>-'FY26 JV Rev'!K6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C52" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D52" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H52" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I52" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q52" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R52" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S52" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T52" s="3">
+        <f>-'FY26 JV Rev'!L2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C53" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D53" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H53" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I53" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K53" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q53" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R53" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S53" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T53" s="3">
+        <f>-'FY26 JV Rev'!L3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C54" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D54" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H54" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I54" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J54" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K54" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q54" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R54" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S54" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T54" s="3">
+        <f>-'FY26 JV Rev'!L4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C55" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D55" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H55" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I55" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K55" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q55" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R55" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S55" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T55" s="3">
+        <f>-'FY26 JV Rev'!L5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C56" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D56" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H56" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I56" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q56" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R56" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S56" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T56" s="3">
+        <f>-'FY26 JV Rev'!L6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C57" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="D57" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A2,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H57" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="I57" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A2)</f>
+        <v/>
+      </c>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N57" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q57" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R57" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="S57" s="1">
+        <f>'FY26 JV Rev'!$A2</f>
+        <v/>
+      </c>
+      <c r="T57" s="3">
+        <f>-'FY26 JV Rev'!M2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C58" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="D58" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A3,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H58" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="I58" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A3)</f>
+        <v/>
+      </c>
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K58" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N58" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O58" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q58" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R58" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="S58" s="1">
+        <f>'FY26 JV Rev'!$A3</f>
+        <v/>
+      </c>
+      <c r="T58" s="3">
+        <f>-'FY26 JV Rev'!M3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C59" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="D59" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A4,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H59" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="I59" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A4)</f>
+        <v/>
+      </c>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K59" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O59" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q59" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R59" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="S59" s="1">
+        <f>'FY26 JV Rev'!$A4</f>
+        <v/>
+      </c>
+      <c r="T59" s="3">
+        <f>-'FY26 JV Rev'!M4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C60" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="D60" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A5,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H60" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="I60" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A5)</f>
+        <v/>
+      </c>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K60" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O60" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q60" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R60" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="S60" s="1">
+        <f>'FY26 JV Rev'!$A5</f>
+        <v/>
+      </c>
+      <c r="T60" s="3">
+        <f>-'FY26 JV Rev'!M5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>37395</v>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="C61" s="1">
+        <f>CONCATENATE("REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="D61" s="1">
+        <f>IFERROR(INDEX('FY26 JV Revenue'!$O$5:$O$9,MATCH('FY26 JV Rev'!$A6,'FY26 JV Revenue'!$A$5:$A$9,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>7868</v>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>Revenue - AUD Million</t>
+        </is>
+      </c>
+      <c r="H61" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="I61" s="1">
+        <f>CONCATENATE("FY26REV_",'FY26 JV Rev'!$A6)</f>
+        <v/>
+      </c>
+      <c r="J61" s="1" t="inlineStr">
+        <is>
+          <t>Downer</t>
+        </is>
+      </c>
+      <c r="K61" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N61" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="O61" s="1" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="Q61" s="1" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="R61" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="S61" s="1">
+        <f>'FY26 JV Rev'!$A6</f>
+        <v/>
+      </c>
+      <c r="T61" s="3">
+        <f>-'FY26 JV Rev'!M6</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33.28515625" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Joint Venture and Associates</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Allied Asphalt</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BIA</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EDI Rail- Bombardier Transportation</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Emulco</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Isaac Asphalt</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <f>B8-SUM(B2:B6)</f>
+        <v/>
+      </c>
+      <c r="C9" s="10">
+        <f>C8-SUM(C2:C6)</f>
+        <v/>
+      </c>
+      <c r="D9" s="10">
+        <f>D8-SUM(D2:D6)</f>
+        <v/>
+      </c>
+      <c r="E9" s="10">
+        <f>E8-SUM(E2:E6)</f>
+        <v/>
+      </c>
+      <c r="F9" s="10">
+        <f>F8-SUM(F2:F6)</f>
+        <v/>
+      </c>
+      <c r="G9" s="10">
+        <f>G8-SUM(G2:G6)</f>
+        <v/>
+      </c>
+      <c r="H9" s="10">
+        <f>H8-SUM(H2:H6)</f>
+        <v/>
+      </c>
+      <c r="I9" s="10">
+        <f>I8-SUM(I2:I6)</f>
+        <v/>
+      </c>
+      <c r="J9" s="10">
+        <f>J8-SUM(J2:J6)</f>
+        <v/>
+      </c>
+      <c r="K9" s="10">
+        <f>K8-SUM(K2:K6)</f>
+        <v/>
+      </c>
+      <c r="L9" s="10">
+        <f>L8-SUM(L2:L6)</f>
+        <v/>
+      </c>
+      <c r="M9" s="10">
+        <f>M8-SUM(M2:M6)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5810,498 +11267,558 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>FY26 JV Revenue — Joint Ventures &amp; Associates (Jul 25 – Jun 26)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Source: "Actual Revenue Jun 26 -unlinked (as at 2026.07.23).xlsx", sheet "FY26 JV Rev", as reported (positive). The Account_Setup_and_Data_Load sheet carries these same amounts NEGATED, to exclude JV revenue from all revenue figures.</t>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Source: sheet "FY26 JV Rev" (copied verbatim into this workbook from "Actual Revenue Jun 26 -unlinked (as at 2026.07.23).xlsx"). Cells below link to it. The Account_Setup_and_Data_Load sheet carries these same amounts NEGATED, to exclude JV revenue from all revenue figures — see "Prep - with formulas" for the row-by-row linking.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Joint Venture and Associates</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>FY26 Total</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>Location Ref</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t>Already in FY26 revenue upload?</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Allied Asphalt</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N5" s="8">
+      <c r="B5" s="15">
+        <f>'FY26 JV Rev'!B2</f>
+        <v/>
+      </c>
+      <c r="C5" s="15">
+        <f>'FY26 JV Rev'!C2</f>
+        <v/>
+      </c>
+      <c r="D5" s="15">
+        <f>'FY26 JV Rev'!D2</f>
+        <v/>
+      </c>
+      <c r="E5" s="15">
+        <f>'FY26 JV Rev'!E2</f>
+        <v/>
+      </c>
+      <c r="F5" s="15">
+        <f>'FY26 JV Rev'!F2</f>
+        <v/>
+      </c>
+      <c r="G5" s="15">
+        <f>'FY26 JV Rev'!G2</f>
+        <v/>
+      </c>
+      <c r="H5" s="15">
+        <f>'FY26 JV Rev'!H2</f>
+        <v/>
+      </c>
+      <c r="I5" s="15">
+        <f>'FY26 JV Rev'!I2</f>
+        <v/>
+      </c>
+      <c r="J5" s="15">
+        <f>'FY26 JV Rev'!J2</f>
+        <v/>
+      </c>
+      <c r="K5" s="15">
+        <f>'FY26 JV Rev'!K2</f>
+        <v/>
+      </c>
+      <c r="L5" s="15">
+        <f>'FY26 JV Rev'!L2</f>
+        <v/>
+      </c>
+      <c r="M5" s="15">
+        <f>'FY26 JV Rev'!M2</f>
+        <v/>
+      </c>
+      <c r="N5" s="15">
         <f>SUM(B5:M5)</f>
         <v/>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="O5" s="14" t="inlineStr">
         <is>
           <t>AASPHT</t>
         </is>
       </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="P5" s="16" t="inlineStr">
         <is>
           <t>No — see note 4</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>BIA</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N6" s="8">
+      <c r="B6" s="15">
+        <f>'FY26 JV Rev'!B3</f>
+        <v/>
+      </c>
+      <c r="C6" s="15">
+        <f>'FY26 JV Rev'!C3</f>
+        <v/>
+      </c>
+      <c r="D6" s="15">
+        <f>'FY26 JV Rev'!D3</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
+        <f>'FY26 JV Rev'!E3</f>
+        <v/>
+      </c>
+      <c r="F6" s="15">
+        <f>'FY26 JV Rev'!F3</f>
+        <v/>
+      </c>
+      <c r="G6" s="15">
+        <f>'FY26 JV Rev'!G3</f>
+        <v/>
+      </c>
+      <c r="H6" s="15">
+        <f>'FY26 JV Rev'!H3</f>
+        <v/>
+      </c>
+      <c r="I6" s="15">
+        <f>'FY26 JV Rev'!I3</f>
+        <v/>
+      </c>
+      <c r="J6" s="15">
+        <f>'FY26 JV Rev'!J3</f>
+        <v/>
+      </c>
+      <c r="K6" s="15">
+        <f>'FY26 JV Rev'!K3</f>
+        <v/>
+      </c>
+      <c r="L6" s="15">
+        <f>'FY26 JV Rev'!L3</f>
+        <v/>
+      </c>
+      <c r="M6" s="15">
+        <f>'FY26 JV Rev'!M3</f>
+        <v/>
+      </c>
+      <c r="N6" s="15">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="O6" s="14" t="inlineStr">
         <is>
           <t>RSV175-1</t>
         </is>
       </c>
-      <c r="P6" s="7" t="inlineStr">
+      <c r="P6" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>EDI Rail- Bombardier Transportation</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N7" s="8">
+      <c r="B7" s="15">
+        <f>'FY26 JV Rev'!B4</f>
+        <v/>
+      </c>
+      <c r="C7" s="15">
+        <f>'FY26 JV Rev'!C4</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>'FY26 JV Rev'!D4</f>
+        <v/>
+      </c>
+      <c r="E7" s="15">
+        <f>'FY26 JV Rev'!E4</f>
+        <v/>
+      </c>
+      <c r="F7" s="15">
+        <f>'FY26 JV Rev'!F4</f>
+        <v/>
+      </c>
+      <c r="G7" s="15">
+        <f>'FY26 JV Rev'!G4</f>
+        <v/>
+      </c>
+      <c r="H7" s="15">
+        <f>'FY26 JV Rev'!H4</f>
+        <v/>
+      </c>
+      <c r="I7" s="15">
+        <f>'FY26 JV Rev'!I4</f>
+        <v/>
+      </c>
+      <c r="J7" s="15">
+        <f>'FY26 JV Rev'!J4</f>
+        <v/>
+      </c>
+      <c r="K7" s="15">
+        <f>'FY26 JV Rev'!K4</f>
+        <v/>
+      </c>
+      <c r="L7" s="15">
+        <f>'FY26 JV Rev'!L4</f>
+        <v/>
+      </c>
+      <c r="M7" s="15">
+        <f>'FY26 JV Rev'!M4</f>
+        <v/>
+      </c>
+      <c r="N7" s="15">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t>ERBT</t>
         </is>
       </c>
-      <c r="P7" s="9" t="inlineStr">
+      <c r="P7" s="16" t="inlineStr">
         <is>
           <t>No — see note 4</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Emulco</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N8" s="8">
+      <c r="B8" s="15">
+        <f>'FY26 JV Rev'!B5</f>
+        <v/>
+      </c>
+      <c r="C8" s="15">
+        <f>'FY26 JV Rev'!C5</f>
+        <v/>
+      </c>
+      <c r="D8" s="15">
+        <f>'FY26 JV Rev'!D5</f>
+        <v/>
+      </c>
+      <c r="E8" s="15">
+        <f>'FY26 JV Rev'!E5</f>
+        <v/>
+      </c>
+      <c r="F8" s="15">
+        <f>'FY26 JV Rev'!F5</f>
+        <v/>
+      </c>
+      <c r="G8" s="15">
+        <f>'FY26 JV Rev'!G5</f>
+        <v/>
+      </c>
+      <c r="H8" s="15">
+        <f>'FY26 JV Rev'!H5</f>
+        <v/>
+      </c>
+      <c r="I8" s="15">
+        <f>'FY26 JV Rev'!I5</f>
+        <v/>
+      </c>
+      <c r="J8" s="15">
+        <f>'FY26 JV Rev'!J5</f>
+        <v/>
+      </c>
+      <c r="K8" s="15">
+        <f>'FY26 JV Rev'!K5</f>
+        <v/>
+      </c>
+      <c r="L8" s="15">
+        <f>'FY26 JV Rev'!L5</f>
+        <v/>
+      </c>
+      <c r="M8" s="15">
+        <f>'FY26 JV Rev'!M5</f>
+        <v/>
+      </c>
+      <c r="N8" s="15">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>EMU</t>
         </is>
       </c>
-      <c r="P8" s="9" t="inlineStr">
+      <c r="P8" s="16" t="inlineStr">
         <is>
           <t>No — see note 4</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Isaac Asphalt</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="8">
+      <c r="B9" s="15">
+        <f>'FY26 JV Rev'!B6</f>
+        <v/>
+      </c>
+      <c r="C9" s="15">
+        <f>'FY26 JV Rev'!C6</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>'FY26 JV Rev'!D6</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
+        <f>'FY26 JV Rev'!E6</f>
+        <v/>
+      </c>
+      <c r="F9" s="15">
+        <f>'FY26 JV Rev'!F6</f>
+        <v/>
+      </c>
+      <c r="G9" s="15">
+        <f>'FY26 JV Rev'!G6</f>
+        <v/>
+      </c>
+      <c r="H9" s="15">
+        <f>'FY26 JV Rev'!H6</f>
+        <v/>
+      </c>
+      <c r="I9" s="15">
+        <f>'FY26 JV Rev'!I6</f>
+        <v/>
+      </c>
+      <c r="J9" s="15">
+        <f>'FY26 JV Rev'!J6</f>
+        <v/>
+      </c>
+      <c r="K9" s="15">
+        <f>'FY26 JV Rev'!K6</f>
+        <v/>
+      </c>
+      <c r="L9" s="15">
+        <f>'FY26 JV Rev'!L6</f>
+        <v/>
+      </c>
+      <c r="M9" s="15">
+        <f>'FY26 JV Rev'!M6</f>
+        <v/>
+      </c>
+      <c r="N9" s="15">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="O9" s="14" t="inlineStr">
         <is>
           <t>ISAAT</t>
         </is>
       </c>
-      <c r="P9" s="9" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr">
         <is>
           <t>No — see note 4</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="17">
         <f>SUM(B5:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="17">
         <f>SUM(C5:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="17">
         <f>SUM(D5:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="17">
         <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="17">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="17">
         <f>SUM(G5:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="17">
         <f>SUM(H5:H9)</f>
         <v/>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="17">
         <f>SUM(I5:I9)</f>
         <v/>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="17">
         <f>SUM(J5:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="17">
         <f>SUM(K5:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="17">
         <f>SUM(L5:L9)</f>
         <v/>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="17">
         <f>SUM(M5:M9)</f>
         <v/>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="17">
         <f>SUM(N5:N9)</f>
         <v/>
       </c>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="6" t="n"/>
+      <c r="O10" s="13" t="n"/>
+      <c r="P10" s="13" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>1. Purpose: JV and associate revenue is to be excluded from all revenue figures. This workbook uploads the JV revenue as negative values against JV-specific locations, so revenue reporting nets to revenue excluding JV revenue.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>2. Locations: per "Extract_for_Locations 1 Oct 25" in the FY26 setup workbook, all five JV revenue locations currently exist in Envizi as "_CLOSED_REV_&lt;name&gt;". They must be reopened / renamed to "REV_&lt;name&gt;" before this file is loaded, otherwise the load will create new locations. All five sit under Group Level 3 classification with Report_Percent 100, so they roll up to group.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>3. Sign convention: the monthly figures on this sheet are JV revenue as reported (positive). The upload sheet carries each one negated. Values of zero are loaded as 0.</t>
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>3. Sign convention: the monthly figures on this sheet are JV revenue as reported (positive), linked from the verbatim "FY26 JV Rev" source sheet. The negation is applied in "Prep - with formulas" (Quantity column: =-'FY26 JV Rev'!&lt;cell&gt;) and the upload sheet carries the resulting values. Values of zero are loaded as 0.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>4. Coverage — CONFIRMED 4 Aug 26: all five JVs are to be uploaded as negatives. For reference: of the five, only BIA appears as a revenue line in the loaded FY26 figures (Account_Setup_and_Data_Load_-_PM&amp;C_REVJUL25toJUN26_Setup.xlsx, and the "FY26 Rev" detail); Allied Asphalt, EDI Rail-Bombardier Transportation, Emulco and Isaac Asphalt do not appear in those figures, so their negatives reduce reported revenue by amounts not previously included (FY26: BIA 69.9 of the 128.4 total; the other four total 58.5: Allied Asphalt 11.6, EDI Rail-Bombardier 35.6, Emulco 4.2, Isaac Asphalt 7.1).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>4a. BIA rounding: BIA totals 70.1 in the loaded FY26 revenue but 69.9 on the "FY26 JV Rev" source sheet (Aug 2.2 vs 2.1, Nov 5.8 vs 5.7). Excluding at the source figures therefore leaves a 0.2 residual for the year. This file uses the source (JV Rev) figures.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>5. Keolis Downer JV — CONFIRMED 4 Aug 26: not excluded. "Rail Services Victoria Pty Ltd" IS in the loaded FY26 revenue figures under REV_Keolis Downer JV (FY26 total 27.3) but is not on the "FY26 JV Rev" source sheet; the source sheet is the agreed definition of JV revenue to exclude, so it stays in revenue.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>6. BIA Location Ref: the extract shows Location Ref "RSV175-1" for _CLOSED_REV_BIA, which looks like a Rail Services Victoria code. Copied faithfully from the extract; worth confirming with the Envizi admin when reopening the locations.</t>
         </is>
@@ -6312,7 +11829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6330,398 +11847,398 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>FY26 JV Revenue Exclusion — Monthly Totals: JV revenue (negated) vs Account Setup</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Each Account Setup monthly total must equal minus the JV revenue for that month.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>JV Revenue (negated)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Account Setup Total</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Row Count (Setup)</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B4" s="8">
-        <f>-SUM('FY26 JV Revenue'!B5:B9)</f>
-        <v/>
-      </c>
-      <c r="C4" s="8">
+      <c r="B4" s="15">
+        <f>-SUM('FY26 JV Rev'!B2:B6)</f>
+        <v/>
+      </c>
+      <c r="C4" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01")</f>
         <v/>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="20">
         <f>ROUND(C4-B4,4)</f>
         <v/>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01")</f>
         <v/>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="14">
         <f>IF(ABS(D4)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="B5" s="8">
-        <f>-SUM('FY26 JV Revenue'!C5:C9)</f>
-        <v/>
-      </c>
-      <c r="C5" s="8">
+      <c r="B5" s="15">
+        <f>-SUM('FY26 JV Rev'!C2:C6)</f>
+        <v/>
+      </c>
+      <c r="C5" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01")</f>
         <v/>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="20">
         <f>ROUND(C5-B5,4)</f>
         <v/>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01")</f>
         <v/>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="14">
         <f>IF(ABS(D5)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B6" s="8">
-        <f>-SUM('FY26 JV Revenue'!D5:D9)</f>
-        <v/>
-      </c>
-      <c r="C6" s="8">
+      <c r="B6" s="15">
+        <f>-SUM('FY26 JV Rev'!D2:D6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01")</f>
         <v/>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="20">
         <f>ROUND(C6-B6,4)</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01")</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="14">
         <f>IF(ABS(D6)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B7" s="8">
-        <f>-SUM('FY26 JV Revenue'!E5:E9)</f>
-        <v/>
-      </c>
-      <c r="C7" s="8">
+      <c r="B7" s="15">
+        <f>-SUM('FY26 JV Rev'!E2:E6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01")</f>
         <v/>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="20">
         <f>ROUND(C7-B7,4)</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01")</f>
         <v/>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="14">
         <f>IF(ABS(D7)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B8" s="8">
-        <f>-SUM('FY26 JV Revenue'!F5:F9)</f>
-        <v/>
-      </c>
-      <c r="C8" s="8">
+      <c r="B8" s="15">
+        <f>-SUM('FY26 JV Rev'!F2:F6)</f>
+        <v/>
+      </c>
+      <c r="C8" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01")</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="20">
         <f>ROUND(C8-B8,4)</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01")</f>
         <v/>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="14">
         <f>IF(ABS(D8)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="B9" s="8">
-        <f>-SUM('FY26 JV Revenue'!G5:G9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="8">
+      <c r="B9" s="15">
+        <f>-SUM('FY26 JV Rev'!G2:G6)</f>
+        <v/>
+      </c>
+      <c r="C9" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01")</f>
         <v/>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="20">
         <f>ROUND(C9-B9,4)</f>
         <v/>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01")</f>
         <v/>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="14">
         <f>IF(ABS(D9)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="B10" s="8">
-        <f>-SUM('FY26 JV Revenue'!H5:H9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="8">
+      <c r="B10" s="15">
+        <f>-SUM('FY26 JV Rev'!H2:H6)</f>
+        <v/>
+      </c>
+      <c r="C10" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01")</f>
         <v/>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="20">
         <f>ROUND(C10-B10,4)</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01")</f>
         <v/>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="14">
         <f>IF(ABS(D10)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="B11" s="8">
-        <f>-SUM('FY26 JV Revenue'!I5:I9)</f>
-        <v/>
-      </c>
-      <c r="C11" s="8">
+      <c r="B11" s="15">
+        <f>-SUM('FY26 JV Rev'!I2:I6)</f>
+        <v/>
+      </c>
+      <c r="C11" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01")</f>
         <v/>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="20">
         <f>ROUND(C11-B11,4)</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01")</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="14">
         <f>IF(ABS(D11)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="B12" s="8">
-        <f>-SUM('FY26 JV Revenue'!J5:J9)</f>
-        <v/>
-      </c>
-      <c r="C12" s="8">
+      <c r="B12" s="15">
+        <f>-SUM('FY26 JV Rev'!J2:J6)</f>
+        <v/>
+      </c>
+      <c r="C12" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01")</f>
         <v/>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="20">
         <f>ROUND(C12-B12,4)</f>
         <v/>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01")</f>
         <v/>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="14">
         <f>IF(ABS(D12)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="B13" s="8">
-        <f>-SUM('FY26 JV Revenue'!K5:K9)</f>
-        <v/>
-      </c>
-      <c r="C13" s="8">
+      <c r="B13" s="15">
+        <f>-SUM('FY26 JV Rev'!K2:K6)</f>
+        <v/>
+      </c>
+      <c r="C13" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01")</f>
         <v/>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="20">
         <f>ROUND(C13-B13,4)</f>
         <v/>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01")</f>
         <v/>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="14">
         <f>IF(ABS(D13)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="B14" s="8">
-        <f>-SUM('FY26 JV Revenue'!L5:L9)</f>
-        <v/>
-      </c>
-      <c r="C14" s="8">
+      <c r="B14" s="15">
+        <f>-SUM('FY26 JV Rev'!L2:L6)</f>
+        <v/>
+      </c>
+      <c r="C14" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01")</f>
         <v/>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="20">
         <f>ROUND(C14-B14,4)</f>
         <v/>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01")</f>
         <v/>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="14">
         <f>IF(ABS(D14)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B15" s="8">
-        <f>-SUM('FY26 JV Revenue'!M5:M9)</f>
-        <v/>
-      </c>
-      <c r="C15" s="8">
+      <c r="B15" s="15">
+        <f>-SUM('FY26 JV Rev'!M2:M6)</f>
+        <v/>
+      </c>
+      <c r="C15" s="15">
         <f>SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01")</f>
         <v/>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="20">
         <f>ROUND(C15-B15,4)</f>
         <v/>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="14">
         <f>COUNTIF(Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01")</f>
         <v/>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="14">
         <f>IF(ABS(D15)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>FY26</t>
         </is>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="17">
         <f>SUM(B4:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="17">
         <f>SUM(C4:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="21">
         <f>ROUND(C16-B16,4)</f>
         <v/>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="13">
         <f>SUM(E4:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="13">
         <f>IF(ABS(D16)&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
@@ -6731,7 +12248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6757,386 +12274,386 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Line-item check: Account Setup upload + source JV revenue = 0 for every JV and every month</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Joint Venture</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Allied Asphalt</t>
         </is>
       </c>
-      <c r="B4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!B5,4)</f>
-        <v/>
-      </c>
-      <c r="C4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!C5,4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!D5,4)</f>
-        <v/>
-      </c>
-      <c r="E4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!E5,4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!F5,4)</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!G5,4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!H5,4)</f>
-        <v/>
-      </c>
-      <c r="I4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!I5,4)</f>
-        <v/>
-      </c>
-      <c r="J4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!J5,4)</f>
-        <v/>
-      </c>
-      <c r="K4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!K5,4)</f>
-        <v/>
-      </c>
-      <c r="L4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!L5,4)</f>
-        <v/>
-      </c>
-      <c r="M4" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Revenue'!M5,4)</f>
-        <v/>
-      </c>
-      <c r="N4" s="7">
+      <c r="B4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!B2,4)</f>
+        <v/>
+      </c>
+      <c r="C4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!C2,4)</f>
+        <v/>
+      </c>
+      <c r="D4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!D2,4)</f>
+        <v/>
+      </c>
+      <c r="E4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!E2,4)</f>
+        <v/>
+      </c>
+      <c r="F4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!F2,4)</f>
+        <v/>
+      </c>
+      <c r="G4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!G2,4)</f>
+        <v/>
+      </c>
+      <c r="H4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!H2,4)</f>
+        <v/>
+      </c>
+      <c r="I4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!I2,4)</f>
+        <v/>
+      </c>
+      <c r="J4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!J2,4)</f>
+        <v/>
+      </c>
+      <c r="K4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!K2,4)</f>
+        <v/>
+      </c>
+      <c r="L4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!L2,4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A4)+'FY26 JV Rev'!M2,4)</f>
+        <v/>
+      </c>
+      <c r="N4" s="14">
         <f>IF(SUMPRODUCT(ABS(B4:M4))&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>BIA</t>
         </is>
       </c>
-      <c r="B5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!B6,4)</f>
-        <v/>
-      </c>
-      <c r="C5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!C6,4)</f>
-        <v/>
-      </c>
-      <c r="D5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!D6,4)</f>
-        <v/>
-      </c>
-      <c r="E5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!E6,4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!F6,4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!G6,4)</f>
-        <v/>
-      </c>
-      <c r="H5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!H6,4)</f>
-        <v/>
-      </c>
-      <c r="I5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!I6,4)</f>
-        <v/>
-      </c>
-      <c r="J5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!J6,4)</f>
-        <v/>
-      </c>
-      <c r="K5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!K6,4)</f>
-        <v/>
-      </c>
-      <c r="L5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!L6,4)</f>
-        <v/>
-      </c>
-      <c r="M5" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Revenue'!M6,4)</f>
-        <v/>
-      </c>
-      <c r="N5" s="7">
+      <c r="B5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!B3,4)</f>
+        <v/>
+      </c>
+      <c r="C5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!C3,4)</f>
+        <v/>
+      </c>
+      <c r="D5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!D3,4)</f>
+        <v/>
+      </c>
+      <c r="E5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!E3,4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!F3,4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!G3,4)</f>
+        <v/>
+      </c>
+      <c r="H5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!H3,4)</f>
+        <v/>
+      </c>
+      <c r="I5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!I3,4)</f>
+        <v/>
+      </c>
+      <c r="J5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!J3,4)</f>
+        <v/>
+      </c>
+      <c r="K5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!K3,4)</f>
+        <v/>
+      </c>
+      <c r="L5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!L3,4)</f>
+        <v/>
+      </c>
+      <c r="M5" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A5)+'FY26 JV Rev'!M3,4)</f>
+        <v/>
+      </c>
+      <c r="N5" s="14">
         <f>IF(SUMPRODUCT(ABS(B5:M5))&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>EDI Rail- Bombardier Transportation</t>
         </is>
       </c>
-      <c r="B6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!B7,4)</f>
-        <v/>
-      </c>
-      <c r="C6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!C7,4)</f>
-        <v/>
-      </c>
-      <c r="D6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!D7,4)</f>
-        <v/>
-      </c>
-      <c r="E6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!E7,4)</f>
-        <v/>
-      </c>
-      <c r="F6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!F7,4)</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!G7,4)</f>
-        <v/>
-      </c>
-      <c r="H6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!H7,4)</f>
-        <v/>
-      </c>
-      <c r="I6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!I7,4)</f>
-        <v/>
-      </c>
-      <c r="J6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!J7,4)</f>
-        <v/>
-      </c>
-      <c r="K6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!K7,4)</f>
-        <v/>
-      </c>
-      <c r="L6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!L7,4)</f>
-        <v/>
-      </c>
-      <c r="M6" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Revenue'!M7,4)</f>
-        <v/>
-      </c>
-      <c r="N6" s="7">
+      <c r="B6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!B4,4)</f>
+        <v/>
+      </c>
+      <c r="C6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!C4,4)</f>
+        <v/>
+      </c>
+      <c r="D6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!D4,4)</f>
+        <v/>
+      </c>
+      <c r="E6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!E4,4)</f>
+        <v/>
+      </c>
+      <c r="F6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!F4,4)</f>
+        <v/>
+      </c>
+      <c r="G6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!G4,4)</f>
+        <v/>
+      </c>
+      <c r="H6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!H4,4)</f>
+        <v/>
+      </c>
+      <c r="I6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!I4,4)</f>
+        <v/>
+      </c>
+      <c r="J6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!J4,4)</f>
+        <v/>
+      </c>
+      <c r="K6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!K4,4)</f>
+        <v/>
+      </c>
+      <c r="L6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!L4,4)</f>
+        <v/>
+      </c>
+      <c r="M6" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A6)+'FY26 JV Rev'!M4,4)</f>
+        <v/>
+      </c>
+      <c r="N6" s="14">
         <f>IF(SUMPRODUCT(ABS(B6:M6))&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Emulco</t>
         </is>
       </c>
-      <c r="B7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!B8,4)</f>
-        <v/>
-      </c>
-      <c r="C7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!C8,4)</f>
-        <v/>
-      </c>
-      <c r="D7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!D8,4)</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!E8,4)</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!F8,4)</f>
-        <v/>
-      </c>
-      <c r="G7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!G8,4)</f>
-        <v/>
-      </c>
-      <c r="H7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!H8,4)</f>
-        <v/>
-      </c>
-      <c r="I7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!I8,4)</f>
-        <v/>
-      </c>
-      <c r="J7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!J8,4)</f>
-        <v/>
-      </c>
-      <c r="K7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!K8,4)</f>
-        <v/>
-      </c>
-      <c r="L7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!L8,4)</f>
-        <v/>
-      </c>
-      <c r="M7" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Revenue'!M8,4)</f>
-        <v/>
-      </c>
-      <c r="N7" s="7">
+      <c r="B7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!B5,4)</f>
+        <v/>
+      </c>
+      <c r="C7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!C5,4)</f>
+        <v/>
+      </c>
+      <c r="D7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!D5,4)</f>
+        <v/>
+      </c>
+      <c r="E7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!E5,4)</f>
+        <v/>
+      </c>
+      <c r="F7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!F5,4)</f>
+        <v/>
+      </c>
+      <c r="G7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!G5,4)</f>
+        <v/>
+      </c>
+      <c r="H7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!H5,4)</f>
+        <v/>
+      </c>
+      <c r="I7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!I5,4)</f>
+        <v/>
+      </c>
+      <c r="J7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!J5,4)</f>
+        <v/>
+      </c>
+      <c r="K7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!K5,4)</f>
+        <v/>
+      </c>
+      <c r="L7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!L5,4)</f>
+        <v/>
+      </c>
+      <c r="M7" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A7)+'FY26 JV Rev'!M5,4)</f>
+        <v/>
+      </c>
+      <c r="N7" s="14">
         <f>IF(SUMPRODUCT(ABS(B7:M7))&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Isaac Asphalt</t>
         </is>
       </c>
-      <c r="B8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!B9,4)</f>
-        <v/>
-      </c>
-      <c r="C8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!C9,4)</f>
-        <v/>
-      </c>
-      <c r="D8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!D9,4)</f>
-        <v/>
-      </c>
-      <c r="E8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!E9,4)</f>
-        <v/>
-      </c>
-      <c r="F8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!F9,4)</f>
-        <v/>
-      </c>
-      <c r="G8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!G9,4)</f>
-        <v/>
-      </c>
-      <c r="H8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!H9,4)</f>
-        <v/>
-      </c>
-      <c r="I8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!I9,4)</f>
-        <v/>
-      </c>
-      <c r="J8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!J9,4)</f>
-        <v/>
-      </c>
-      <c r="K8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!K9,4)</f>
-        <v/>
-      </c>
-      <c r="L8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!L9,4)</f>
-        <v/>
-      </c>
-      <c r="M8" s="13">
-        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Revenue'!M9,4)</f>
-        <v/>
-      </c>
-      <c r="N8" s="7">
+      <c r="B8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-07-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!B6,4)</f>
+        <v/>
+      </c>
+      <c r="C8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-08-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!C6,4)</f>
+        <v/>
+      </c>
+      <c r="D8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-09-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!D6,4)</f>
+        <v/>
+      </c>
+      <c r="E8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-10-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!E6,4)</f>
+        <v/>
+      </c>
+      <c r="F8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-11-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!F6,4)</f>
+        <v/>
+      </c>
+      <c r="G8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2025-12-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!G6,4)</f>
+        <v/>
+      </c>
+      <c r="H8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-01-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!H6,4)</f>
+        <v/>
+      </c>
+      <c r="I8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-02-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!I6,4)</f>
+        <v/>
+      </c>
+      <c r="J8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-03-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!J6,4)</f>
+        <v/>
+      </c>
+      <c r="K8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-04-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!K6,4)</f>
+        <v/>
+      </c>
+      <c r="L8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-05-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!L6,4)</f>
+        <v/>
+      </c>
+      <c r="M8" s="20">
+        <f>ROUND(SUMIFS(Account_Setup_and_Data_Load!$T$2:$T$61,Account_Setup_and_Data_Load!$L$2:$L$61,"2026-06-01",Account_Setup_and_Data_Load!$R$2:$R$61,$A8)+'FY26 JV Rev'!M6,4)</f>
+        <v/>
+      </c>
+      <c r="N8" s="14">
         <f>IF(SUMPRODUCT(ABS(B8:M8))&lt;=0.001,"OK","MISMATCH")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="13">
         <f>IF(SUMPRODUCT(ABS(B4:M8))&lt;=0.001,"ALL OK","MISMATCH")</f>
         <v/>
       </c>
